--- a/docs/review-blackboard-22-cases.xlsx
+++ b/docs/review-blackboard-22-cases.xlsx
@@ -7,11 +7,11 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="22题复核" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="裁决说明" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="冻结题集21" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="冻结记录" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'22题复核'!$A$1:$L$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'冻结题集21'!$A$1:$N$22</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -66,7 +66,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -75,6 +75,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -445,21 +448,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L23"/>
+  <dimension ref="A1:N22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="52" customWidth="1" min="3" max="3"/>
-    <col width="46" customWidth="1" min="4" max="4"/>
-    <col width="34" customWidth="1" min="5" max="5"/>
-    <col width="6" customWidth="1" min="6" max="6"/>
-    <col width="40" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
-    <col width="11" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="30" customWidth="1" min="12" max="12"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
+    <col width="46" customWidth="1" min="5" max="5"/>
+    <col width="32" customWidth="1" min="6" max="6"/>
+    <col width="6" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
+    <col width="9" customWidth="1" min="9" max="9"/>
+    <col width="9" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="26" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -470,57 +475,67 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>角色</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>类型</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>判定链（前序真实提问）</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>判分题（逐字，不要改标点）</t>
-        </is>
-      </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>判分题（逐字）</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>出处</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>轮数</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>判定要点</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>16k 有效样本</t>
-        </is>
-      </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
+          <t>臂2有效</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>臂3有效</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
           <t>干跑:指针行</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>干跑:子图est</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>你的裁定</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>备注/替换为</t>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>裁定</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>备注</t>
         </is>
       </c>
     </row>
@@ -532,45 +547,59 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
+          <t>能力题</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
           <t>A 序数/指示代词指涉</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>什么是乘潮水位？ → 重力式码头的设计应符合哪条规范要求？ → 依据《海港总体设计规范》确定设计船型尺度的原则是什么？ → 某5万吨级散货船，船长230米，满载吃水12.8米，试计算码头前沿设计水深。 → 你好，在么</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>刚才第二条提到的规范，具体说了什么？</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>chat-amin-test-0929  seq=20</t>
         </is>
       </c>
-      <c r="F2" s="2" t="n">
+      <c r="G2" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>正确指认「第二条」并按该轮答案复述规范要求；题面有歧义，可判作废</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="n">
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="J2" s="2" t="n">
+      <c r="L2" s="2" t="n">
         <v>31</v>
       </c>
-      <c r="K2" s="2" t="inlineStr"/>
-      <c r="L2" s="2" t="inlineStr"/>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>保留</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -580,45 +609,59 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
+          <t>能力题</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
           <t>A 序数/指示代词指涉</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>什么是乘潮水位？ → 重力式码头抗滑稳定安全系数应如何取值？ → 码头前沿设计水深由哪几部分组成？ → 某3万吨级杂货船，满载吃水10.5米，试计算码头前沿设计水深。 → 你好，在么</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>刚才第2题说的安全系数，具体数值是多少？</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>chat-mumg89qg-c14jeu  seq=21</t>
         </is>
       </c>
-      <c r="F3" s="2" t="n">
+      <c r="G3" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>给出第 2 题安全系数的具体数值 + 出处；只答「需查表」= 部分对</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="n">
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="J3" s="2" t="n">
+      <c r="L3" s="2" t="n">
         <v>40</v>
       </c>
-      <c r="K3" s="2" t="inlineStr"/>
-      <c r="L3" s="2" t="inlineStr"/>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>保留</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -628,45 +671,59 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
+          <t>能力题</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
           <t>A 序数/指示代词指涉</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>什么是乘潮水位？ → 重力式码头抗滑稳定安全系数应如何取值？ → 码头前沿设计水深由哪几部分组成？ → 某3万吨级杂货船，满载吃水10.5米，试计算码头前沿设计水深。 → 你好，在么 → 刚才第2题说的安全系数，具体数值是多少？</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>那抗倾稳定呢？</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>chat-mumg89qg-c14jeu  seq=25</t>
         </is>
       </c>
-      <c r="F4" s="2" t="n">
+      <c r="G4" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>承接上轮抗滑口径，给抗倾安全取值与出处</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="n">
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="J4" s="2" t="n">
+      <c r="L4" s="2" t="n">
         <v>76</v>
       </c>
-      <c r="K4" s="2" t="inlineStr"/>
-      <c r="L4" s="2" t="inlineStr"/>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>保留</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -676,45 +733,59 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
+          <t>能力题</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
           <t>A 序数/指示代词指涉</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>什么是乘潮水位？ → 重力式码头抗滑稳定安全系数应如何取值？ → 码头前沿设计水深由哪几部分组成？ → 某3万吨级杂货船，满载吃水10.5米，试计算码头前沿设计水深。 → 你好，在么 → 刚才第2题说的安全系数，具体数值是多少？ → 那抗倾稳定呢？ → 现在知识库里一共有多少篇文档？ → 这些文档里，港口工程类的规范有哪些？</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>把第4题的计算过程再详细讲一遍</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>chat-mumg89qg-c14jeu  seq=37</t>
         </is>
       </c>
-      <c r="F5" s="2" t="n">
+      <c r="G5" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>步骤完整（含各富裕深度分量）+ 数值与第 4 轮一致</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="n">
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="J5" s="2" t="n">
+      <c r="L5" s="2" t="n">
         <v>79</v>
       </c>
-      <c r="K5" s="2" t="inlineStr"/>
-      <c r="L5" s="2" t="inlineStr"/>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>保留</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -724,45 +795,59 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
+          <t>能力题</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
           <t>A 序数/指示代词指涉</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>堤顶高程怎么计算 → 想知道的 → 想的 → 好的 → 乘潮水位怎么计算</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>刚才第二个问题说了什么</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>chat-municgem-i8m5b5  seq=21</t>
         </is>
       </c>
-      <c r="F6" s="2" t="n">
+      <c r="G6" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>机制自检题：复述第 2 轮提问原文「想知道的」+ 当时回答要点；不计入 §7.1 分母</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="n">
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="J6" s="2" t="n">
+      <c r="L6" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="K6" s="2" t="inlineStr"/>
-      <c r="L6" s="2" t="inlineStr"/>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>保留</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -772,45 +857,59 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
+          <t>能力题</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
           <t>A 序数/指示代词指涉</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>桥梁支座病害有哪些类型？</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>请把上面提到的每一类支座病害的成因、检查方法和处治工艺都展开详细说明</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>chat-munhocfh-r5cbj6  seq=5</t>
         </is>
       </c>
-      <c r="F7" s="2" t="n">
+      <c r="G7" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>类别齐全（来自第 1 轮答案清单），每类含成因/检查/处治</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="n">
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J7" s="2" t="n">
+      <c r="L7" s="2" t="n">
         <v>56</v>
       </c>
-      <c r="K7" s="2" t="inlineStr"/>
-      <c r="L7" s="2" t="inlineStr"/>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>保留</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -820,45 +919,59 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
+          <t>能力题</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
           <t>A 序数/指示代词指涉</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>乘潮水位怎么计算 → 是的 → “乘潮累积频率”的具体统计</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>上一条里为什么没有一个引用，都是[K6] [K7]?</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>docs:chat-muf9m7b1-9ohqmp  seq=13</t>
         </is>
       </c>
-      <c r="F8" s="2" t="n">
+      <c r="G8" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>指认上一条回答里的引用标记分布并解释</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="n">
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J8" s="2" t="n">
+      <c r="L8" s="2" t="n">
         <v>102</v>
       </c>
-      <c r="K8" s="2" t="inlineStr"/>
-      <c r="L8" s="2" t="inlineStr"/>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>保留</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
@@ -868,45 +981,59 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
+          <t>能力题</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
           <t>B 值复用/跨轮计算</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="D9" s="3" t="inlineStr">
         <is>
           <t>查设计船型尺度表，DWT=40000 杂货船对应的满载吃水 T 这一列的值</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="E9" s="3" t="inlineStr">
         <is>
           <t>帮我算一下：先查出 DWT=40000 杂货船的满载吃水 T，再加上 0.5 米富裕深度，总共多少？</t>
         </is>
       </c>
-      <c r="E9" s="3" t="inlineStr">
+      <c r="F9" s="3" t="inlineStr">
         <is>
           <t>chat-mupdlobp-22wezs  seq=5</t>
         </is>
       </c>
-      <c r="F9" s="3" t="n">
+      <c r="G9" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="G9" s="3" t="inlineStr">
+      <c r="H9" s="3" t="inlineStr">
         <is>
           <t>复用上一轮 T 值 + 给出 T+0.5 结果；T 与表不一致 = ❌</t>
         </is>
       </c>
-      <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t>否（16k 不触发压缩，臂1≡臂2）</t>
-        </is>
-      </c>
-      <c r="I9" s="3" t="n">
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="J9" s="3" t="n">
+      <c r="L9" s="3" t="n">
         <v>40</v>
       </c>
-      <c r="K9" s="3" t="inlineStr"/>
-      <c r="L9" s="3" t="inlineStr"/>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>保留</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
@@ -916,45 +1043,59 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
+          <t>能力题</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
           <t>B 值复用/跨轮计算</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="D10" s="3" t="inlineStr">
         <is>
           <t>查设计船型尺度表，DWT=40000 杂货船对应的满载吃水 T 这一列的值 → 帮我算一下：先查出 DWT=40000 杂货船的满载吃水 T，再加上 0.5 米富…</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="E10" s="3" t="inlineStr">
         <is>
           <t>某港区设计高水位 3.5m，设计低水位 0.5m，DWT=40000 杂货船，计算航道通航水深</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="F10" s="3" t="inlineStr">
         <is>
           <t>chat-mupecuyb-zu4x4l  seq=9</t>
         </is>
       </c>
-      <c r="F10" s="3" t="n">
+      <c r="G10" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="G10" s="3" t="inlineStr">
+      <c r="H10" s="3" t="inlineStr">
         <is>
           <t>公式 + 各分量取值 + 结果 + 规范依据</t>
         </is>
       </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>否（16k 不触发压缩，臂1≡臂2）</t>
-        </is>
-      </c>
-      <c r="I10" s="3" t="n">
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="J10" s="3" t="n">
+      <c r="L10" s="3" t="n">
         <v>40</v>
       </c>
-      <c r="K10" s="3" t="inlineStr"/>
-      <c r="L10" s="3" t="inlineStr"/>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>保留</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -964,45 +1105,59 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
+          <t>能力题</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
           <t>B 值复用/跨轮计算</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>查设计船型尺度表，DWT=40000 杂货船对应的满载吃水 T 这一列的值 → 帮我算一下：先查出 DWT=40000 杂货船的满载吃水 T，再加上 0.5 米富… → 某港区设计高水位 3.5m，设计低水位 0.5m，DWT=40000 杂货船，计算…</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>查一下杂货船设计船型尺度，DWT=40000 的满载吃水</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>chat-mupecuyb-zu4x4l  seq=13</t>
         </is>
       </c>
-      <c r="F11" s="2" t="n">
+      <c r="G11" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>直接给出 T 值、不重复检索错表</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="n">
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J11" s="2" t="n">
+      <c r="L11" s="2" t="n">
         <v>40</v>
       </c>
-      <c r="K11" s="2" t="inlineStr"/>
-      <c r="L11" s="2" t="inlineStr"/>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>保留</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -1012,579 +1167,685 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
+          <t>能力题</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
           <t>B 值复用/跨轮计算</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>依据《海港总体设计规范》确定20000吨级散货船的设计船型尺度 → 5000吨级散货船的码头前沿水深富裕高度取值是多少？ → 《港口工程荷载规范》中，船舶荷载应如何取值？ → 液化天然气码头的设计船型尺度如何确定？ → 《内河通航标准》里，航道等级与设计船型尺度怎么对应？ → 什么是乘潮水位？ → 什么是设计低水位？ → 防波堤的主要作用是什么？</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>某5000吨级散货船，满载吃水T=9.8m，试计算码头前沿设计水深</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>chat-muj4iiw7-2jwt5v  seq=41</t>
         </is>
       </c>
-      <c r="F12" s="2" t="n">
+      <c r="G12" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>分量齐（龙骨下富裕深度等）+ 结果正确 + 出处</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="n">
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="J12" s="2" t="n">
+      <c r="L12" s="2" t="n">
         <v>40</v>
       </c>
-      <c r="K12" s="2" t="inlineStr"/>
-      <c r="L12" s="2" t="inlineStr"/>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>保留</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>B5</t>
+          <t>C1</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>B 值复用/跨轮计算</t>
+          <t>能力题</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>什么是乘潮水位？ → 重力式码头抗滑稳定安全系数应如何取值？ → 码头前沿设计水深由哪几部分组成？</t>
+          <t>C 条款回引</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>某3万吨级杂货船，满载吃水10.5米，试计算码头前沿设计水深。</t>
+          <t>「在疏浚工程设计中，选择乘潮水位还是设计低水位对工程投资的具体影响」 → 具体差多少 → 想 → 航道设计水深表中富裕深度的取值是多少」</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>chat-mumg89qg-c14jeu  seq=13</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="n">
+          <t>JTS 181 里乘潮水位累积频率表怎么规定的</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>chat-muh62u2n-94kq9h  seq=17</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>给出条文/表号 + 频率取值口径</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>同 B4 口径</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J13" s="2" t="n">
-        <v>127</v>
-      </c>
-      <c r="K13" s="2" t="inlineStr"/>
-      <c r="L13" s="2" t="inlineStr"/>
+      <c r="L13" s="2" t="n">
+        <v>248</v>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>保留</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
+          <t>能力题</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
           <t>C 条款回引</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>「在疏浚工程设计中，选择乘潮水位还是设计低水位对工程投资的具体影响」 → 具体差多少 → 想 → 航道设计水深表中富裕深度的取值是多少」</t>
-        </is>
-      </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>JTS 181 里乘潮水位累积频率表怎么规定的</t>
+          <t>乘潮水位怎么计算 → 是的</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>chat-muh62u2n-94kq9h  seq=17</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>给出条文/表号 + 频率取值口径</t>
-        </is>
+          <t>“乘潮累积频率”的具体统计</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>docs:chat-muf9m7b1-9ohqmp  seq=11</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J14" s="2" t="n">
-        <v>248</v>
-      </c>
-      <c r="K14" s="2" t="inlineStr"/>
-      <c r="L14" s="2" t="inlineStr"/>
+          <t>统计步骤完整（样本、年限、保证率）</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L14" s="2" t="n">
+        <v>150</v>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>保留</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>C2</t>
+          <t>C3</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
+          <t>能力题</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
           <t>C 条款回引</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>乘潮水位怎么计算 → 是的</t>
-        </is>
-      </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>“乘潮累积频率”的具体统计</t>
+          <t>乘潮水位是什么 → 继续 → 是的 → 想知道</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>docs:chat-muf9m7b1-9ohqmp  seq=11</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="n">
+          <t>“设计使用年限”在《港口工程荷载规范》或《码头结构设计规范》中的具体取值要求</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>docs:chat-mufo8ffw-jirdxg  seq=17</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>规范名 + 年限取值</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>统计步骤完整（样本、年限、保证率）</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J15" s="2" t="n">
-        <v>150</v>
-      </c>
-      <c r="K15" s="2" t="inlineStr"/>
-      <c r="L15" s="2" t="inlineStr"/>
+      <c r="L15" s="2" t="n">
+        <v>269</v>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>保留</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>C3</t>
+          <t>C4</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
+          <t>能力题</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
           <t>C 条款回引</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>乘潮水位是什么 → 继续 → 是的 → 想知道</t>
-        </is>
-      </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>“设计使用年限”在《港口工程荷载规范》或《码头结构设计规范》中的具体取值要求</t>
+          <t>乘潮水位是什么 → 继续 → 是的 → 想知道 → “设计使用年限”在《港口工程荷载规范》或《码头结构设计规范》中的具体取值要求</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>docs:chat-mufo8ffw-jirdxg  seq=17</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="n">
+          <t>超过设计使用年限后，码头结构进行继续使用或改造的具体评估要求</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>docs:chat-mufo8ffw-jirdxg  seq=21</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>承接 C3 结论给出评估要求（检测项/评定方法）</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>规范名 + 年限取值</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J16" s="2" t="n">
-        <v>269</v>
-      </c>
-      <c r="K16" s="2" t="inlineStr"/>
-      <c r="L16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="n">
+        <v>170</v>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>保留</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>C4</t>
+          <t>C5</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
+          <t>能力题</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
           <t>C 条款回引</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>乘潮水位是什么 → 继续 → 是的 → 想知道 → “设计使用年限”在《港口工程荷载规范》或《码头结构设计规范》中的具体取值要求</t>
-        </is>
-      </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>超过设计使用年限后，码头结构进行继续使用或改造的具体评估要求</t>
+          <t>依据《海港总体设计规范》确定20000吨级散货船的设计船型尺度 → 5000吨级散货船的码头前沿水深富裕高度取值是多少？ → 《港口工程荷载规范》中，船舶荷载应如何取值？ → 液化天然气码头的设计船型尺度如何确定？ → 《内河通航标准》里，航道等级与设计船型尺度怎么对应？ → 什么是乘潮水位？ → 什么是设计低水位？ → 防波堤的主要作用是什么？ → 某5000吨级散货船，满载吃水T=9.8m，试计算码头前沿设计水深</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>docs:chat-mufo8ffw-jirdxg  seq=21</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>承接 C3 结论给出评估要求（检测项/评定方法）</t>
-        </is>
+          <t>重力式码头抗滑稳定性验算应符合哪条规范要求？</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>chat-muj4iiw7-2jwt5v  seq=44</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="n">
+        <v>10</v>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J17" s="2" t="n">
-        <v>170</v>
-      </c>
-      <c r="K17" s="2" t="inlineStr"/>
-      <c r="L17" s="2" t="inlineStr"/>
+          <t>规范名 + 条款号 + 安全系数</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="L17" s="2" t="n">
+        <v>125</v>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>保留</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>C5</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>C6</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>对照题</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
         <is>
           <t>C 条款回引</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>依据《海港总体设计规范》确定20000吨级散货船的设计船型尺度 → 5000吨级散货船的码头前沿水深富裕高度取值是多少？ → 《港口工程荷载规范》中，船舶荷载应如何取值？ → 液化天然气码头的设计船型尺度如何确定？ → 《内河通航标准》里，航道等级与设计船型尺度怎么对应？ → 什么是乘潮水位？ → 什么是设计低水位？ → 防波堤的主要作用是什么？ → 某5000吨级散货船，满载吃水T=9.8m，试计算码头前沿设计水深</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>重力式码头抗滑稳定性验算应符合哪条规范要求？</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>chat-muj4iiw7-2jwt5v  seq=44</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>规范名 + 条款号 + 安全系数</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J18" s="2" t="n">
-        <v>125</v>
-      </c>
-      <c r="K18" s="2" t="inlineStr"/>
-      <c r="L18" s="2" t="inlineStr"/>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>（无前序轮，单轮题）</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>沉箱干舷高度应满足哪条规范？</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>p0-accept-2  seq=1</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>给出规范出处与限值。**预注册对照题**：单轮无判定链、图上无节点——预期三臂 prompt 等价，任何差异都是干扰证据（用来验「图模式不伤单轮题」）</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t>保留（对照）</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>C6</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>C 条款回引</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t>（无前序轮，单轮题）</t>
-        </is>
-      </c>
-      <c r="D19" s="3" t="inlineStr">
-        <is>
-          <t>沉箱干舷高度应满足哪条规范？</t>
-        </is>
-      </c>
-      <c r="E19" s="3" t="inlineStr">
-        <is>
-          <t>p0-accept-2  seq=1</t>
-        </is>
-      </c>
-      <c r="F19" s="3" t="n">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>能力题</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>D 跨轮综合</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>「在疏浚工程设计中，选择乘潮水位还是设计低水位对工程投资的具体影响」</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>具体差多少</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>chat-muh62u2n-94kq9h  seq=5</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>给出可核对的数量口径，或明确说明证据缺失项</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="G19" s="3" t="inlineStr">
-        <is>
-          <t>给出规范出处与限值</t>
-        </is>
-      </c>
-      <c r="H19" s="3" t="inlineStr">
-        <is>
-          <t>否（16k 不触发压缩，臂1≡臂2）</t>
-        </is>
-      </c>
-      <c r="I19" s="3" t="n">
+      <c r="L19" s="2" t="n">
+        <v>58</v>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>保留</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>D2</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>能力题</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>D 跨轮综合</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>疏浚底高程怎么计算</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>内河与外海有区别么</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>docs:chat-mufmsfto-no2hkt  seq=6</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>至少在基准水位/方法/规范依据三项上说清区别</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="J19" s="3" t="n">
+      <c r="L20" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="M20" s="3" t="inlineStr">
+        <is>
+          <t>保留</t>
+        </is>
+      </c>
+      <c r="N20" s="3" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>D3</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>能力题</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>D 跨轮综合</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>乘潮水位怎么计算 → 好的，继续 → 一个8m的立杆，如果需要做基础，这个基础应该是多大？</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>基础的混凝土用多少标号的</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>docs:chat-mufn0n8m-0i0wkg  seq=22</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>引用上一轮给的基础尺寸前提 + 标号建议</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="L21" s="2" t="n">
+        <v>142</v>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>保留</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>D4</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>对照题</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>D 跨轮综合</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>依据《海港总体设计规范》确定20000吨级散货船的设计船型尺度</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>5000吨级散货船的码头前沿水深富裕高度取值是多少？</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>chat-muj4iiw7-2jwt5v  seq=5</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>表值 + 出处。**预注册对照题**：历史里没有被引用条款 → 图空 → 护栏生效（臂 3 不移除证据）——预期三臂 prompt 等价，臂 3 不劣化</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="K19" s="3" t="inlineStr"/>
-      <c r="L19" s="3" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>D1</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>D 跨轮综合</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>「在疏浚工程设计中，选择乘潮水位还是设计低水位对工程投资的具体影响」</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>具体差多少</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>chat-muh62u2n-94kq9h  seq=5</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>给出可核对的数量口径，或明确说明证据缺失项</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J20" s="2" t="n">
-        <v>58</v>
-      </c>
-      <c r="K20" s="2" t="inlineStr"/>
-      <c r="L20" s="2" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t>D2</t>
-        </is>
-      </c>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>D 跨轮综合</t>
-        </is>
-      </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>疏浚底高程怎么计算</t>
-        </is>
-      </c>
-      <c r="D21" s="3" t="inlineStr">
-        <is>
-          <t>内河与外海有区别么</t>
-        </is>
-      </c>
-      <c r="E21" s="3" t="inlineStr">
-        <is>
-          <t>docs:chat-mufmsfto-no2hkt  seq=6</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="G21" s="3" t="inlineStr">
-        <is>
-          <t>至少在基准水位/方法/规范依据三项上说清区别</t>
-        </is>
-      </c>
-      <c r="H21" s="3" t="inlineStr">
-        <is>
-          <t>否（16k 不触发压缩，臂1≡臂2）</t>
-        </is>
-      </c>
-      <c r="I21" s="3" t="n">
+      <c r="L22" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="J21" s="3" t="n">
-        <v>32</v>
-      </c>
-      <c r="K21" s="3" t="inlineStr"/>
-      <c r="L21" s="3" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>D3</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>D 跨轮综合</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>乘潮水位怎么计算 → 好的，继续 → 一个8m的立杆，如果需要做基础，这个基础应该是多大？</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>基础的混凝土用多少标号的</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>docs:chat-mufn0n8m-0i0wkg  seq=22</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>引用上一轮给的基础尺寸前提 + 标号建议</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J22" s="2" t="n">
-        <v>142</v>
-      </c>
-      <c r="K22" s="2" t="inlineStr"/>
-      <c r="L22" s="2" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="3" t="inlineStr">
-        <is>
-          <t>D4</t>
-        </is>
-      </c>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>D 跨轮综合</t>
-        </is>
-      </c>
-      <c r="C23" s="3" t="inlineStr">
-        <is>
-          <t>依据《海港总体设计规范》确定20000吨级散货船的设计船型尺度</t>
-        </is>
-      </c>
-      <c r="D23" s="3" t="inlineStr">
-        <is>
-          <t>5000吨级散货船的码头前沿水深富裕高度取值是多少？</t>
-        </is>
-      </c>
-      <c r="E23" s="3" t="inlineStr">
-        <is>
-          <t>chat-muj4iiw7-2jwt5v  seq=5</t>
-        </is>
-      </c>
-      <c r="F23" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="G23" s="3" t="inlineStr">
-        <is>
-          <t>表值 + 出处</t>
-        </is>
-      </c>
-      <c r="H23" s="3" t="inlineStr">
-        <is>
-          <t>否（16k 不触发压缩，臂1≡臂2）</t>
-        </is>
-      </c>
-      <c r="I23" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" s="3" t="inlineStr"/>
-      <c r="L23" s="3" t="inlineStr"/>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
+          <t>保留（对照）</t>
+        </is>
+      </c>
+      <c r="N22" s="3" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L23"/>
+  <autoFilter ref="A1:N22"/>
   <dataValidations count="1">
-    <dataValidation sqref="K2:K23" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
-      <formula1>"保留,修改,删除"</formula1>
+    <dataValidation sqref="M2:M22" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"保留,保留（对照）,修改,删除"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1597,17 +1858,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="92" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="96" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t>对话黑板 M0 主集复核 · 说明</t>
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>对话黑板 M0 题集冻结记录（2026-10-05）</t>
         </is>
       </c>
       <c r="B1" s="2" t="inlineStr"/>
@@ -1620,103 +1881,103 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>1853dc29052bbb4006cc3d95f26fa7a940b8089d514490c4967473d3df58d58f</t>
+          <t>05264ca6f0dd88da6f5138e838eba78872be15234139c6a2ff537fcf468b1a7c</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>保真</t>
+          <t>构成</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>22/22 与 chat.sqlite 的 (session_id, seq) 处 user 消息逐字一致</t>
+          <t>21 题 = 19 能力题 + 2 对照题（原 22 题减去 B5 去重）</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>判定链口径</t>
+          <t>题面</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>该会话中 seq 更小的真实提问；判分时按 arms §3 逐一走完这些轮再问判分题</t>
+          <t>一字未改（只删除 B5）；逐题与 chat.sqlite 的 (session_id, seq) 处 user 消息逐字一致</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>有效样本（16k）</t>
+          <t>有效样本</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>17/22（黄色行＝不触发压缩，臂1≡臂2，对指针零信息量）</t>
+          <t>臂2 vs 臂1 = 16/21；臂3 vs 臂1 = 19/21；核心（臂3 vs 臂2）= 17</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr"/>
-      <c r="B6" s="2" t="inlineStr"/>
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>口径①</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>预算 16k est（生产 QA 档）；8k 敏感性跑为探索性，不进主结论</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>怎么标</t>
+          <t>口径②</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>在「22题复核」表 K 列选 保留 / 修改 / 删除；要改就写在 L 列</t>
+          <t>判定链照真实会话走全部真实提问（含寒暄/碎轮）</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>怎么冻结</t>
+          <t>口径③</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>回表给我 → 我更新 cases.py → 重跑保真测试 → 新指纹写入 arms §6</t>
+          <t>对照题不计入能力分母；三臂应等价，差异即干扰证据</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr"/>
-      <c r="B9" s="2" t="inlineStr"/>
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>删除记录</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>B5（与 B4 同口径近重复，chat-mumg89qg-c14jeu seq=13）</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>同时请裁</t>
+          <t>核对</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>① 有效样本口径：接受黄色行不计，或对它们另设更小预算重跑</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr"/>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>② 是否跑臂 1 基线快照 + 三臂判分（真实模型，限流 1 并发）</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr"/>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>③ 发版号（与复核并行；发版后 nightly 才成有效护栏）</t>
+          <t>pytest services/evals-core/tests/test_blackboard_m0.py；本表由 .dsh-scratch/gen_case_review.py 复现</t>
         </is>
       </c>
     </row>
